--- a/artfynd/A 24156-2026 artfynd.xlsx
+++ b/artfynd/A 24156-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84435405</v>
+        <v>4950524</v>
       </c>
       <c r="B2" t="n">
-        <v>97728</v>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hamnäsudden  Almbacken, Hls</t>
+          <t>(14H7a31), Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593974</v>
+        <v>594048</v>
       </c>
       <c r="R2" t="n">
-        <v>6787856</v>
+        <v>6787705</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,24 +738,19 @@
           <t>Skog</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>BFO200006263019</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-06-26</t>
+          <t>1996-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-06-26</t>
+          <t>1996-09-20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Observatör: Bosse Forsling</t>
+          <t>140770311 / HEPA NOB / Ej bedömd (0)  / OBJ.AREA:0,5 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,32 +764,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsdunge intill byn</t>
+          <t>Ädellövskog /</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Wannberg</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Björn Wannberg</t>
+          <t>Christer Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Hälsinglands flora (2019)</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84435398</v>
+        <v>5241410</v>
       </c>
       <c r="B3" t="n">
-        <v>107179</v>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220015</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,17 +817,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hamnäsudden  Almbacken, Hls</t>
+          <t>(14H7a31), Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593974</v>
+        <v>594048</v>
       </c>
       <c r="R3" t="n">
-        <v>6787856</v>
+        <v>6787705</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,24 +849,19 @@
           <t>Skog</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>BFO200006263019</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-06-26</t>
+          <t>1996-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-06-26</t>
+          <t>1996-09-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Observatör: Bosse Forsling</t>
+          <t>140770311 / ACTA SPI / Ej bedömd (0)  / OBJ.AREA:0,5 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,371 +875,23 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skogsdunge intill byn</t>
+          <t>Ädellövskog /</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Björn Wannberg</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Björn Wannberg</t>
+          <t>Christer Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>84435399</v>
-      </c>
-      <c r="B4" t="n">
-        <v>106284</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Hamnäsudden  Almbacken, Hls</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>593974</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6787856</v>
-      </c>
-      <c r="S4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Söderhamn</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Skog</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>BFO200006263019</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2000-06-26</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2000-06-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Observatör: Bosse Forsling</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsdunge intill byn</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Björn Wannberg</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Via Björn Wannberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>84435400</v>
-      </c>
-      <c r="B5" t="n">
-        <v>104127</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Hamnäsudden  Almbacken, Hls</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>593974</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6787856</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Söderhamn</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Skog</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>BFO200006263019</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2000-06-26</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2000-06-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Observatör: Bosse Forsling</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Skogsdunge intill byn</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Björn Wannberg</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Via Björn Wannberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>84435403</v>
-      </c>
-      <c r="B6" t="n">
-        <v>102903</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>223246</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Hamnäsudden  Almbacken, Hls</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>593974</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6787856</v>
-      </c>
-      <c r="S6" t="n">
-        <v>100</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Söderhamn</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Skog</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>BFO200006263019</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2000-06-26</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2000-06-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Observatör: Bosse Forsling</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Skogsdunge intill byn</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Björn Wannberg</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Via Björn Wannberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 24156-2026 artfynd.xlsx
+++ b/artfynd/A 24156-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4950524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5241410</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>